--- a/artfynd/A 3383-2026 artfynd.xlsx
+++ b/artfynd/A 3383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113654401</v>
+        <v>124802488</v>
       </c>
       <c r="B2" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gäddlokan (Gäddlokan), Dlr</t>
+          <t>Hjortronmyran, Hjortronmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534571</v>
+        <v>534715</v>
       </c>
       <c r="R2" t="n">
-        <v>6728606</v>
+        <v>6728901</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,58 +791,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115225404</v>
+        <v>116613861</v>
       </c>
       <c r="B3" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Erik-Mårsmyran (Erik-Mårsmyran), Dlr</t>
+          <t>Erik-Mårsmyran, Erik-Mårsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535055</v>
+        <v>535110</v>
       </c>
       <c r="R3" t="n">
-        <v>6728688</v>
+        <v>6728813</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116613861</v>
+        <v>121248386</v>
       </c>
       <c r="B4" t="n">
-        <v>91721</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,42 +914,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Erik-Mårsmyran (Erik-Mårsmyran), Dlr</t>
+          <t>Erik-Mårsmyran, Erik-Mårsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535110</v>
+        <v>534786</v>
       </c>
       <c r="R4" t="n">
-        <v>6728813</v>
+        <v>6728791</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +973,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ingen fågel utan födosökshack i äldre tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,61 +994,76 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Morän</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Moraine # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Nils Spross</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Nils Spross</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121245693</v>
+        <v>121245704</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1118,21 +1121,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Morän</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Moraine</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,40 +1137,40 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121245704</v>
+        <v>121245693</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1241,6 +1229,21 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Morän</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Moraine</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1253,6 +1256,338 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113654401</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gäddlokan, Gäddlokan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>534571</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6728606</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115225404</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Erik-Mårsmyran, Erik-Mårsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>535055</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6728688</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116612621</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hjortronmyran, Hjortronmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6728932</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3383-2026 artfynd.xlsx
+++ b/artfynd/A 3383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124802488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116613861</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121248386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121245704</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121245693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113654401</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115225404</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1588,8 +1628,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116612621</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>